--- a/data/valuations/MCD/MCD_modelo_valoracion.xlsx
+++ b/data/valuations/MCD/MCD_modelo_valoracion.xlsx
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02443002692242816</v>
+        <v>0.09961299699606976</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02443002692242816</v>
+        <v>0.09961299699606976</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.02443002692242816</v>
+        <v>0.09961299699606976</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.02443002692242816</v>
+        <v>0.09961299699606976</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.02443002692242816</v>
+        <v>0.09961299699606976</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01943002692242815</v>
+        <v>0.09461299699606976</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01943002692242815</v>
+        <v>0.09461299699606976</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01943002692242815</v>
+        <v>0.09461299699606976</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.01943002692242815</v>
+        <v>0.09461299699606976</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.01943002692242815</v>
+        <v>0.09461299699606976</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.02943002692242816</v>
+        <v>0.1046129969960698</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.02943002692242816</v>
+        <v>0.1046129969960698</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.02943002692242816</v>
+        <v>0.1046129969960698</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.02943002692242816</v>
+        <v>0.1046129969960698</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.02943002692242816</v>
+        <v>0.1046129969960698</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.05809999999999999</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.07809999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>305.9</v>
+        <v>307.14</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/305.9-1</f>
+        <f>C33/307.14-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.03809999999999999</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.04809999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.05809999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.07809999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.0881</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.09809999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
